--- a/Foundation Model Project/统计.xlsx
+++ b/Foundation Model Project/统计.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RayShape\Desktop\Foundation Model Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Young\Desktop\GitHub\Miscellaneous-documents\Foundation Model Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD3058B-9031-4E16-9161-68281F53D4F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69FF5F26-3574-48AE-BBE8-66974CABECFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2D超声FM" sheetId="1" r:id="rId1"/>
     <sheet name="医学3DFM" sheetId="2" r:id="rId2"/>
+    <sheet name="多模态" sheetId="4" r:id="rId3"/>
+    <sheet name="其他图像" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="93">
   <si>
     <t>文章</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -241,12 +243,275 @@
     <t>https://doi.org/10.48550/arXiv.2510.22990</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>A foundation model for enhancing magnetic resonance images and downstream segmentation, registration and diagnostic tasks</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nature biomedical engineering</t>
+  </si>
+  <si>
+    <t>MRI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1038/s41551-024-01283-7</t>
+  </si>
+  <si>
+    <t>BME-X.pdf</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>来自公共数据集的的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 10963 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>张图像用于训练，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">2448 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>张刻意受损的图像测试性能</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>两个DU-Net串联，输入低质量图像，预测每个体素的组织标签，输出高质量图像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A foundation model for generalizable cancer diagnosis and survival prediction from histopathological images</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nature communications</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>病理组织图像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1177万</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1038/s41467-025-57587-y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Histopathological.pdf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UltraSAM: A foundational medical ultrasound segmentation model with limited training data</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.eswa.2025.130223</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Expert Systems with Applications</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6种解剖结构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基于SAM的核心框架修改编码器，是基于预训练模型（SAM）的有监督微调模型，780个含标注的图像用于微调，261/262个含标注的图像用于验证/测试，其余图像用作外部测试集来测试泛化能力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UltraSAM.pdf</t>
+  </si>
+  <si>
+    <t>Multi-Organ Foundation Model for Universal Ultrasound Image Segmentation With Task Prompt and Anatomical Prior</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IEEE TRANSACTIONS ON MEDICAL IMAGING</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个器官的超声图像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/TMI.2024.3472672</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MOFO.pdf</t>
+  </si>
+  <si>
+    <r>
+      <t>Transformer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>编码器</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>+CNN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>解码器</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>+10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>器官初始文本提示词嵌入
+属于有监督学习，细分任务（分割）下的Foundation Model</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pattern Recognition</t>
+  </si>
+  <si>
+    <t>Dual-masked contrastive learning based hypergraph foundation model for 
+whole slide images</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.patcog.2025.111995</t>
+  </si>
+  <si>
+    <t>DMCL-HFM.pdf</t>
+  </si>
+  <si>
+    <t>对比学习</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70w以上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Procedia Computer Science</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Medformer: A Multitask Multimodal Foundational Model for Medical Imaging</t>
+  </si>
+  <si>
+    <t>基于Transformer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.procs.2025.09.163</t>
+  </si>
+  <si>
+    <t>Medformer.pdf</t>
+  </si>
+  <si>
+    <t>多模态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MedMNIST 基准多模态数据集</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100w以上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.compbiomed.2025.110583</t>
+  </si>
+  <si>
+    <t>Radio DINO: A foundation model for advanced radiomics and AI-driven medical imaging analysis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Computers in Biology and Medicine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vision Transformer（ViT）为骨干的DINO网络</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Radio DINO.pdf</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -281,6 +546,25 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -303,7 +587,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -315,6 +599,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -599,7 +890,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U16"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
     <col min="3" max="3" width="20.44140625" customWidth="1"/>
@@ -610,7 +901,7 @@
     <col min="10" max="10" width="41.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -642,7 +933,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" ht="41.4">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -685,7 +976,7 @@
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
     </row>
-    <row r="3" spans="1:21" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" ht="41.4">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
@@ -719,7 +1010,7 @@
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
     </row>
-    <row r="4" spans="1:21" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="27.6">
       <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
@@ -755,7 +1046,7 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
     </row>
-    <row r="5" spans="1:21" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="41.4">
       <c r="A5" s="1" t="s">
         <v>33</v>
       </c>
@@ -791,7 +1082,7 @@
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
     </row>
-    <row r="6" spans="1:21" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="41.4">
       <c r="A6" s="1" t="s">
         <v>39</v>
       </c>
@@ -821,8 +1112,8 @@
       </c>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:21" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:21" ht="40.200000000000003" customHeight="1">
+      <c r="A7" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B7" s="1">
@@ -847,7 +1138,65 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" ht="55.2">
+      <c r="A8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="1">
+        <v>2025</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8">
+        <v>15</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8">
+        <v>16820</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="50.4">
+      <c r="A9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="1">
+        <v>2025</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F9">
+        <v>7039</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21">
       <c r="I16" s="2"/>
     </row>
   </sheetData>
@@ -863,18 +1212,322 @@
     <hyperlink ref="H6" r:id="rId8" xr:uid="{C38CDC44-4CA9-45D6-8895-515E1F67CE86}"/>
     <hyperlink ref="I6" r:id="rId9" xr:uid="{2BF83CFA-B92D-480B-91A7-E7AB05859F91}"/>
     <hyperlink ref="H7" r:id="rId10" xr:uid="{EF8C57B3-1EAE-4A67-B607-362FC20DA02A}"/>
+    <hyperlink ref="H8" r:id="rId11" xr:uid="{6A94FE47-B705-47AF-9FEA-72862A7A4E0D}"/>
+    <hyperlink ref="I8" r:id="rId12" xr:uid="{55744B75-CE29-47C0-B846-5D353FDE0E1E}"/>
+    <hyperlink ref="H9" r:id="rId13" xr:uid="{5F35F654-6175-49E0-97E8-2EF63921BF1E}"/>
+    <hyperlink ref="I9" r:id="rId14" xr:uid="{6182084F-FC16-4B27-97A6-C526D1F02D2F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId11"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId15"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A164D7C2-5B09-4A90-82A2-A3E66DF7E93F}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="35.33203125" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" customWidth="1"/>
+    <col min="6" max="6" width="18.109375" customWidth="1"/>
+    <col min="7" max="7" width="19.44140625" customWidth="1"/>
+    <col min="8" max="8" width="20.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="69.599999999999994" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="1">
+        <v>26.6</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J2" s="1"/>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{CD393B97-19A5-4FF5-8513-21A444E8935C}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04FB60FA-F5EF-4D5B-BD52-DB33AAEC1E1C}">
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="27.5546875" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" customWidth="1"/>
+    <col min="5" max="5" width="17.77734375" customWidth="1"/>
+    <col min="7" max="7" width="24.88671875" customWidth="1"/>
+    <col min="8" max="8" width="29.77734375" customWidth="1"/>
+    <col min="9" max="9" width="15.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="41.4">
+      <c r="A2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="1">
+        <v>2025</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="55.2">
+      <c r="A3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{B82956FC-0A51-417C-BF4F-F7F48D8AF2B1}"/>
+    <hyperlink ref="I3" r:id="rId2" xr:uid="{ADD7B32D-2D2A-4361-8AB6-4E8E6D60D8EE}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{521B7F00-3993-4F69-903E-B0C354333E79}">
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="48.33203125" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" customWidth="1"/>
+    <col min="7" max="7" width="26.88671875" customWidth="1"/>
+    <col min="8" max="8" width="31.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="69">
+      <c r="A2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="1">
+        <v>2025</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="1">
+        <v>15.7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" spans="1:10" ht="41.4">
+      <c r="A3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="1">
+        <v>2025</v>
+      </c>
+      <c r="C3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3">
+        <v>3000</v>
+      </c>
+      <c r="G3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{4B88348F-4085-45DF-BD33-E5EC9FFEA977}"/>
+    <hyperlink ref="I3" r:id="rId2" xr:uid="{6399A6B3-45AB-4A8E-848E-7620E62E091D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+</worksheet>
 </file>
--- a/Foundation Model Project/统计.xlsx
+++ b/Foundation Model Project/统计.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Young\Desktop\GitHub\Miscellaneous-documents\Foundation Model Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\Miscellaneous-documents\Foundation Model Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69FF5F26-3574-48AE-BBE8-66974CABECFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDCE6E87-AD68-4D85-8C2D-BE9BB5B17A4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="99">
   <si>
     <t>文章</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -476,10 +476,6 @@
     <t>Medformer.pdf</t>
   </si>
   <si>
-    <t>多模态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>MedMNIST 基准多模态数据集</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -505,13 +501,40 @@
   </si>
   <si>
     <t>Radio DINO.pdf</t>
+  </si>
+  <si>
+    <t>A vision–language foundation model for precision oncology</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>病理组织图像和文本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5000 万病理图像和 10 亿病理相关文本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1038/s41586-024-08378-w</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第一阶段对文本和图像各自做掩码建模学习，第二阶段使用对比学习实现图像和文本对齐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A vision–language foundation model for precision oncology.pdf</t>
+  </si>
+  <si>
+    <t>多模态数据集</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -587,7 +610,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -607,6 +630,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -890,7 +916,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U16"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
     <col min="3" max="3" width="20.44140625" customWidth="1"/>
@@ -901,7 +927,7 @@
     <col min="10" max="10" width="41.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -933,7 +959,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="41.4">
+    <row r="2" spans="1:21" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -976,7 +1002,7 @@
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
     </row>
-    <row r="3" spans="1:21" ht="41.4">
+    <row r="3" spans="1:21" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
@@ -1010,7 +1036,7 @@
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
     </row>
-    <row r="4" spans="1:21" ht="27.6">
+    <row r="4" spans="1:21" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
@@ -1046,7 +1072,7 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
     </row>
-    <row r="5" spans="1:21" ht="41.4">
+    <row r="5" spans="1:21" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>33</v>
       </c>
@@ -1082,7 +1108,7 @@
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
     </row>
-    <row r="6" spans="1:21" ht="41.4">
+    <row r="6" spans="1:21" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>39</v>
       </c>
@@ -1112,7 +1138,7 @@
       </c>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:21" ht="40.200000000000003" customHeight="1">
+    <row r="7" spans="1:21" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>45</v>
       </c>
@@ -1138,7 +1164,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="55.2">
+    <row r="8" spans="1:21" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>62</v>
       </c>
@@ -1167,7 +1193,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="50.4">
+    <row r="9" spans="1:21" ht="50.4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>68</v>
       </c>
@@ -1196,7 +1222,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="1:21">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="I16" s="2"/>
     </row>
   </sheetData>
@@ -1225,7 +1251,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A164D7C2-5B09-4A90-82A2-A3E66DF7E93F}">
   <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.33203125" customWidth="1"/>
     <col min="3" max="3" width="21.5546875" customWidth="1"/>
@@ -1234,7 +1260,7 @@
     <col min="8" max="8" width="20.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1266,7 +1292,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="69.599999999999994" customHeight="1">
+    <row r="2" spans="1:10" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>49</v>
       </c>
@@ -1309,7 +1335,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04FB60FA-F5EF-4D5B-BD52-DB33AAEC1E1C}">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.5546875" customWidth="1"/>
     <col min="3" max="3" width="17.33203125" customWidth="1"/>
@@ -1319,7 +1345,7 @@
     <col min="9" max="9" width="15.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1351,7 +1377,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="41.4">
+    <row r="2" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>81</v>
       </c>
@@ -1365,7 +1391,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>79</v>
@@ -1380,33 +1406,33 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="55.2">
+    <row r="3" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B3">
         <v>2025</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D3">
         <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="I3" s="5" t="s">
         <v>91</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1421,16 +1447,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{521B7F00-3993-4F69-903E-B0C354333E79}">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.33203125" customWidth="1"/>
     <col min="3" max="3" width="21.5546875" customWidth="1"/>
     <col min="7" max="7" width="26.88671875" customWidth="1"/>
     <col min="8" max="8" width="31.77734375" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1462,7 +1489,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="69">
+    <row r="2" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>56</v>
       </c>
@@ -1492,7 +1519,7 @@
       </c>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" ht="41.4">
+    <row r="3" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>75</v>
       </c>
@@ -1519,6 +1546,35 @@
       </c>
       <c r="I3" s="5" t="s">
         <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2025</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="3">
+        <v>48.5</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1526,8 +1582,10 @@
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{4B88348F-4085-45DF-BD33-E5EC9FFEA977}"/>
     <hyperlink ref="I3" r:id="rId2" xr:uid="{6399A6B3-45AB-4A8E-848E-7620E62E091D}"/>
+    <hyperlink ref="H4" r:id="rId3" xr:uid="{9F7B8496-ACAB-4E7D-8826-E6FBD63EC3B7}"/>
+    <hyperlink ref="I4" r:id="rId4" xr:uid="{7C0630CB-1F01-46AA-B08D-EC20844377AD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>